--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1777-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1777-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7816B27-2899-4079-AAFA-FAECBD8133A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42D78664-6084-4DDB-A5A4-D19745E4D4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{3797C138-E197-421A-BED8-CF2C37945164}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{21354420-83E7-4793-BDE6-14C25C5C9E63}"/>
   </bookViews>
   <sheets>
     <sheet name="1777-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1469,26 +1469,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1DC601-3072-486F-9081-C76EF97B577B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96BC4C1F-1125-4BF3-BA0D-B42F4083ABBC}">
   <dimension ref="A1:X29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="4" width="6.625" customWidth="1"/>
-    <col min="5" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
-    <col min="7" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1522,7 +1520,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1558,7 +1556,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1610,7 +1608,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1678,7 +1676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1750,7 +1748,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1822,7 +1820,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1894,7 +1892,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1966,7 +1964,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2038,7 +2036,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2110,7 +2108,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2182,7 +2180,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2254,7 +2252,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2326,7 +2324,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2398,7 +2396,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2470,7 +2468,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2542,7 +2540,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2614,7 +2612,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2686,7 +2684,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2758,7 +2756,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2830,7 +2828,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2902,7 +2900,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2974,7 +2972,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -3046,7 +3044,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2005</v>
       </c>
@@ -3118,7 +3116,7 @@
         <v>9.2200000000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2004</v>
       </c>
@@ -3190,7 +3188,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2003</v>
       </c>
@@ -3262,7 +3260,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2002</v>
       </c>
@@ -3334,7 +3332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2001</v>
       </c>
@@ -3406,7 +3404,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33" t="s">
         <v>49</v>
       </c>
